--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate/AGGREGATE_CIUDAD MOLINA BASKET.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate/AGGREGATE_CIUDAD MOLINA BASKET.xlsx
@@ -3075,92 +3075,92 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>#37 C. TOLEDO ZAMORA</t>
+          <t>#88 J. TAVELLI</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H18" t="n">
         <v>10</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K18" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
         <v>6</v>
       </c>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>10</v>
-      </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="U18" t="n">
+        <v>2</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
         <v>5</v>
       </c>
-      <c r="V18" t="n">
-        <v>1</v>
-      </c>
-      <c r="W18" t="n">
-        <v>11</v>
-      </c>
       <c r="X18" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z18" t="n">
         <v>6</v>
       </c>
-      <c r="Z18" t="n">
-        <v>13</v>
-      </c>
       <c r="AA18" t="n">
-        <v>0.462</v>
+        <v>0.5</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -3169,115 +3169,115 @@
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>56:26</t>
+          <t>52:43</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>24.04</v>
+        <v>26.72</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.469</v>
+        <v>0.281</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.543</v>
+        <v>0.437</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.04</v>
+        <v>0.711</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.042</v>
+        <v>0.187</v>
       </c>
       <c r="AT18" t="n">
         <v>0.625</v>
       </c>
       <c r="AU18" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>16</v>
+        <v>3.2</v>
       </c>
       <c r="AW18" t="n">
-        <v>17</v>
+        <v>4.6</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.197</v>
+        <v>0.235</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.098</v>
+        <v>0.017</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.186</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="BA18" t="n">
-        <v>0.026</v>
+        <v>0.167</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>#88 J. TAVELLI</t>
+          <t>Equip</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>5</v>
       </c>
-      <c r="H19" t="n">
-        <v>10</v>
-      </c>
-      <c r="I19" t="n">
-        <v>13</v>
-      </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>7</v>
       </c>
-      <c r="K19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -3286,46 +3286,46 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3334,7 +3334,7 @@
         <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -3343,225 +3343,225 @@
         <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>52:43</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>26.72</v>
+        <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.281</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.437</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.711</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.187</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.235</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.07199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="K20" t="n">
+        <v>52</v>
+      </c>
+      <c r="L20" t="n">
+        <v>29</v>
+      </c>
+      <c r="M20" t="n">
+        <v>8</v>
+      </c>
+      <c r="N20" t="n">
         <v>5</v>
       </c>
-      <c r="L20" t="n">
-        <v>7</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>0.523</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>400:00</t>
         </is>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>172.84</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>0.463</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>0.517</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>0.891</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>0.139</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>0.336</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>0.958</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>5.083</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>6.042</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>0.124</v>
       </c>
       <c r="BA20" t="n">
         <v>0</v>
@@ -3570,122 +3570,122 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Rival</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D21" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E21" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="F21" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G21" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H21" t="n">
         <v>41</v>
       </c>
       <c r="I21" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J21" t="n">
         <v>23</v>
       </c>
       <c r="K21" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="L21" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="M21" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="N21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P21" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>17</v>
+      </c>
+      <c r="R21" t="n">
+        <v>53</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>89</v>
+      </c>
+      <c r="U21" t="n">
+        <v>16</v>
+      </c>
+      <c r="V21" t="n">
+        <v>23</v>
+      </c>
+      <c r="W21" t="n">
         <v>24</v>
       </c>
-      <c r="Q21" t="n">
-        <v>13</v>
-      </c>
-      <c r="R21" t="n">
-        <v>51</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>86</v>
-      </c>
-      <c r="U21" t="n">
-        <v>13</v>
-      </c>
-      <c r="V21" t="n">
-        <v>12</v>
-      </c>
-      <c r="W21" t="n">
-        <v>22</v>
-      </c>
       <c r="X21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y21" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Z21" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.523</v>
+        <v>0.543</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
       </c>
       <c r="AC21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
         <v>9</v>
       </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2</v>
-      </c>
       <c r="AF21" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.5</v>
+        <v>0.529</v>
       </c>
       <c r="AH21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI21" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.133</v>
+        <v>0.273</v>
       </c>
       <c r="AK21" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AL21" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.38</v>
+        <v>0.234</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
@@ -3693,40 +3693,40 @@
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>172.84</v>
+        <v>178.4</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.463</v>
+        <v>0.433</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.517</v>
+        <v>0.492</v>
       </c>
       <c r="AR21" t="n">
-        <v>0.891</v>
+        <v>0.846</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.139</v>
+        <v>0.14</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.336</v>
+        <v>0.323</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.958</v>
+        <v>0.92</v>
       </c>
       <c r="AV21" t="n">
-        <v>5.083</v>
+        <v>5.08</v>
       </c>
       <c r="AW21" t="n">
-        <v>6.042</v>
+        <v>6</v>
       </c>
       <c r="AX21" t="n">
         <v>0.2</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.067</v>
+        <v>0.076</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.124</v>
+        <v>0.133</v>
       </c>
       <c r="BA21" t="n">
         <v>0</v>
@@ -3735,166 +3735,166 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>2</v>
       </c>
       <c r="C22" t="n">
-        <v>151</v>
+        <v>25</v>
       </c>
       <c r="D22" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="F22" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="H22" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="I22" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="L22" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>10</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>17</v>
+      </c>
+      <c r="U22" t="n">
+        <v>5</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
         <v>11</v>
       </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>4</v>
-      </c>
-      <c r="P22" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="X22" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>56:26</t>
+        </is>
+      </c>
+      <c r="AO22" t="n">
+        <v>24.04</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW22" t="n">
         <v>17</v>
       </c>
-      <c r="R22" t="n">
-        <v>53</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>89</v>
-      </c>
-      <c r="U22" t="n">
-        <v>16</v>
-      </c>
-      <c r="V22" t="n">
-        <v>23</v>
-      </c>
-      <c r="W22" t="n">
-        <v>24</v>
-      </c>
-      <c r="X22" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>46</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0.543</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0.529</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0.273</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>47</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>0.234</v>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>400:00</t>
-        </is>
-      </c>
-      <c r="AO22" t="n">
-        <v>178.4</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>0.492</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>0.846</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0.323</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>6</v>
-      </c>
       <c r="AX22" t="n">
-        <v>0.2</v>
+        <v>0.197</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.076</v>
+        <v>0.098</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0.133</v>
+        <v>0.186</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="23">
@@ -5609,92 +5609,92 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#37 C. TOLEDO ZAMORA (Per Game)</t>
+          <t>#88 J. TAVELLI (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>2</v>
       </c>
       <c r="C34" t="n">
-        <v>12.5</v>
+        <v>9.5</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="E34" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="F34" t="n">
         <v>0.5</v>
       </c>
       <c r="G34" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="H34" t="n">
         <v>5</v>
       </c>
       <c r="I34" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" t="n">
+        <v>3</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
         <v>8</v>
       </c>
-      <c r="J34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K34" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L34" t="n">
+      <c r="U34" t="n">
+        <v>1</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X34" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z34" t="n">
         <v>3</v>
       </c>
-      <c r="M34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>5</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>17</v>
-      </c>
-      <c r="U34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W34" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="X34" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>6.5</v>
-      </c>
       <c r="AA34" t="n">
-        <v>0.462</v>
+        <v>0.5</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -5703,237 +5703,237 @@
         <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>28:13</t>
+          <t>26:21</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>12.02</v>
+        <v>13.36</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.469</v>
+        <v>0.281</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.543</v>
+        <v>0.437</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.04</v>
+        <v>0.711</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.042</v>
+        <v>0.187</v>
       </c>
       <c r="AT34" t="n">
         <v>0.625</v>
       </c>
       <c r="AU34" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AV34" t="n">
-        <v>16</v>
+        <v>3.2</v>
       </c>
       <c r="AW34" t="n">
-        <v>17</v>
+        <v>4.6</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.197</v>
+        <v>0.235</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.098</v>
+        <v>0.017</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0.186</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="BA34" t="n">
-        <v>0.026</v>
+        <v>0.167</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#88 J. TAVELLI (Per Game)</t>
+          <t>CLUB BALONCESTO TOLEDO BASKET (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>2</v>
       </c>
       <c r="C35" t="n">
-        <v>9.5</v>
+        <v>12.5</v>
       </c>
       <c r="D35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G35" t="n">
         <v>1.5</v>
-      </c>
-      <c r="E35" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G35" t="n">
-        <v>2.5</v>
       </c>
       <c r="H35" t="n">
         <v>5</v>
       </c>
       <c r="I35" t="n">
+        <v>8</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K35" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L35" t="n">
+        <v>3</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>5</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>17</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W35" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="X35" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z35" t="n">
         <v>6.5</v>
       </c>
-      <c r="J35" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K35" t="n">
-        <v>2</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M35" t="n">
+      <c r="AA35" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI35" t="n">
         <v>1.5</v>
       </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1</v>
-      </c>
-      <c r="R35" t="n">
-        <v>3</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>8</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X35" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AK35" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>26:21</t>
+          <t>28:13</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>13.36</v>
+        <v>12.02</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.281</v>
+        <v>0.469</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.437</v>
+        <v>0.543</v>
       </c>
       <c r="AR35" t="n">
-        <v>0.711</v>
+        <v>1.04</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.187</v>
+        <v>0.042</v>
       </c>
       <c r="AT35" t="n">
         <v>0.625</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AV35" t="n">
-        <v>3.2</v>
+        <v>16</v>
       </c>
       <c r="AW35" t="n">
-        <v>4.6</v>
+        <v>17</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.235</v>
+        <v>0.197</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.017</v>
+        <v>0.098</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.186</v>
       </c>
       <c r="BA35" t="n">
-        <v>0.167</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="36">
